--- a/카테고리번호_기본.xlsx
+++ b/카테고리번호_기본.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jihun\Desktop\완성\★update\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10C374C3-33CB-4AFC-866B-33E9FE5D815D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3986036C-234B-4F37-8369-2C92E75645D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9915" yWindow="2730" windowWidth="26160" windowHeight="17550" xr2:uid="{C7C98F17-E1B4-4C04-891E-7391719F0528}"/>
+    <workbookView xWindow="-27870" yWindow="2220" windowWidth="24225" windowHeight="17550" xr2:uid="{C7C98F17-E1B4-4C04-891E-7391719F0528}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -53,10 +53,6 @@
   </si>
   <si>
     <t>모나마켓</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>맹지선</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -157,6 +153,10 @@
   </si>
   <si>
     <t>김다혜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>곽충현</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -649,82 +649,82 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" t="s">
+        <v>13</v>
+      </c>
+      <c r="S1" t="s">
+        <v>14</v>
+      </c>
+      <c r="T1" t="s">
+        <v>15</v>
+      </c>
+      <c r="U1" t="s">
+        <v>17</v>
+      </c>
+      <c r="V1" t="s">
+        <v>18</v>
+      </c>
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="O1" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R1" t="s">
-        <v>14</v>
-      </c>
-      <c r="S1" t="s">
-        <v>15</v>
-      </c>
-      <c r="T1" t="s">
-        <v>16</v>
-      </c>
-      <c r="U1" t="s">
-        <v>18</v>
-      </c>
-      <c r="V1" t="s">
-        <v>19</v>
-      </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
         <v>28</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.3">
@@ -839,7 +839,7 @@
         <v>470</v>
       </c>
       <c r="F3" s="3">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="G3" s="3">
         <v>112</v>
@@ -934,7 +934,7 @@
         <v>485</v>
       </c>
       <c r="F4" s="3">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="G4" s="3">
         <v>112</v>
@@ -1029,7 +1029,7 @@
         <v>395</v>
       </c>
       <c r="F5" s="3">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="G5" s="3">
         <v>112</v>
@@ -1124,7 +1124,7 @@
         <v>389</v>
       </c>
       <c r="F6" s="3">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="G6" s="3">
         <v>112</v>
@@ -1314,7 +1314,7 @@
         <v>550</v>
       </c>
       <c r="F8" s="3">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="G8" s="3">
         <v>113</v>
@@ -1409,7 +1409,7 @@
         <v>406</v>
       </c>
       <c r="F9" s="3">
-        <v>42</v>
+        <v>106</v>
       </c>
       <c r="G9" s="3">
         <v>113</v>
@@ -1504,7 +1504,7 @@
         <v>305</v>
       </c>
       <c r="F10" s="3">
-        <v>42</v>
+        <v>106</v>
       </c>
       <c r="G10" s="3">
         <v>113</v>
@@ -1599,7 +1599,7 @@
         <v>406</v>
       </c>
       <c r="F11" s="3">
-        <v>42</v>
+        <v>106</v>
       </c>
       <c r="G11" s="3">
         <v>113</v>
@@ -1694,7 +1694,7 @@
         <v>550</v>
       </c>
       <c r="F12" s="3">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="G12" s="3">
         <v>113</v>
@@ -1789,7 +1789,7 @@
         <v>404</v>
       </c>
       <c r="F13" s="3">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="G13" s="3">
         <v>113</v>
@@ -1884,7 +1884,7 @@
         <v>402</v>
       </c>
       <c r="F14" s="3">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="G14" s="3">
         <v>113</v>
@@ -1979,7 +1979,7 @@
         <v>404</v>
       </c>
       <c r="F15" s="3">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="G15" s="3">
         <v>113</v>
@@ -2074,7 +2074,7 @@
         <v>529</v>
       </c>
       <c r="F16" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G16" s="3">
         <v>115</v>
@@ -2264,7 +2264,7 @@
         <v>418</v>
       </c>
       <c r="F18" s="3">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="G18" s="3">
         <v>114</v>
@@ -2359,7 +2359,7 @@
         <v>587</v>
       </c>
       <c r="F19" s="3">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="G19" s="3">
         <v>114</v>
@@ -2454,7 +2454,7 @@
         <v>408</v>
       </c>
       <c r="F20" s="3">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="G20" s="3">
         <v>114</v>
@@ -2549,7 +2549,7 @@
         <v>429</v>
       </c>
       <c r="F21" s="3">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="G21" s="3">
         <v>114</v>
@@ -2644,7 +2644,7 @@
         <v>429</v>
       </c>
       <c r="F22" s="3">
-        <v>43</v>
+        <v>128</v>
       </c>
       <c r="G22" s="3">
         <v>114</v>
@@ -2739,7 +2739,7 @@
         <v>427</v>
       </c>
       <c r="F23" s="3">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="G23" s="3">
         <v>114</v>
@@ -2834,7 +2834,7 @@
         <v>519</v>
       </c>
       <c r="F24" s="3">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="G24" s="3">
         <v>115</v>
@@ -2929,7 +2929,7 @@
         <v>556</v>
       </c>
       <c r="F25" s="3">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G25" s="3">
         <v>116</v>
@@ -3024,7 +3024,7 @@
         <v>128</v>
       </c>
       <c r="F26" s="3">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="G26" s="3">
         <v>125</v>
@@ -3119,7 +3119,7 @@
         <v>136</v>
       </c>
       <c r="F27" s="3">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G27" s="3">
         <v>124</v>
@@ -3214,7 +3214,7 @@
         <v>246</v>
       </c>
       <c r="F28" s="3">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="G28" s="3">
         <v>126</v>
@@ -3309,7 +3309,7 @@
         <v>105</v>
       </c>
       <c r="F29" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G29" s="3">
         <v>127</v>
@@ -3404,7 +3404,7 @@
         <v>118</v>
       </c>
       <c r="F30" s="3">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="G30" s="3">
         <v>111</v>
@@ -3499,7 +3499,7 @@
         <v>123</v>
       </c>
       <c r="F31" s="3">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="G31" s="3">
         <v>119</v>
@@ -3594,7 +3594,7 @@
         <v>259</v>
       </c>
       <c r="F32" s="3">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="G32" s="3">
         <v>120</v>
@@ -3689,7 +3689,7 @@
         <v>119</v>
       </c>
       <c r="F33" s="3">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="G33" s="3">
         <v>122</v>
@@ -3784,7 +3784,7 @@
         <v>397</v>
       </c>
       <c r="F34" s="3">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="G34" s="3">
         <v>128</v>
@@ -3879,7 +3879,7 @@
         <v>260</v>
       </c>
       <c r="F35" s="3">
-        <v>58</v>
+        <v>136</v>
       </c>
       <c r="G35" s="3">
         <v>128</v>
@@ -3974,7 +3974,7 @@
         <v>145</v>
       </c>
       <c r="F36" s="3">
-        <v>58</v>
+        <v>137</v>
       </c>
       <c r="G36" s="3">
         <v>129</v>
@@ -4069,7 +4069,7 @@
         <v>250</v>
       </c>
       <c r="F37" s="3">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="G37" s="3">
         <v>130</v>
@@ -4164,7 +4164,7 @@
         <v>121</v>
       </c>
       <c r="F38" s="3">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="G38" s="3">
         <v>121</v>
@@ -4259,7 +4259,7 @@
         <v>124</v>
       </c>
       <c r="F39" s="3">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="G39" s="3">
         <v>123</v>
@@ -4354,7 +4354,7 @@
         <v>194</v>
       </c>
       <c r="F40" s="3">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="G40" s="3">
         <v>131</v>
@@ -4449,7 +4449,7 @@
         <v>686</v>
       </c>
       <c r="F41" s="3">
-        <v>60</v>
+        <v>157</v>
       </c>
       <c r="G41" s="3">
         <v>131</v>
@@ -4544,7 +4544,7 @@
         <v>685</v>
       </c>
       <c r="F42" s="3">
-        <v>60</v>
+        <v>158</v>
       </c>
       <c r="G42" s="3">
         <v>131</v>
@@ -4639,7 +4639,7 @@
         <v>484</v>
       </c>
       <c r="F43" s="3">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="G43" s="3">
         <v>131</v>
@@ -4734,7 +4734,7 @@
         <v>687</v>
       </c>
       <c r="F44" s="3">
-        <v>60</v>
+        <v>156</v>
       </c>
       <c r="G44" s="3">
         <v>131</v>
@@ -4829,7 +4829,7 @@
         <v>483</v>
       </c>
       <c r="F45" s="3">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="G45" s="3">
         <v>131</v>
@@ -5019,7 +5019,7 @@
         <v>104</v>
       </c>
       <c r="F47" s="3">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="G47" s="3">
         <v>117</v>
@@ -5114,7 +5114,7 @@
         <v>151</v>
       </c>
       <c r="F48" s="3">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="G48" s="3">
         <v>117</v>
@@ -5209,7 +5209,7 @@
         <v>262</v>
       </c>
       <c r="F49" s="3">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="G49" s="3">
         <v>117</v>
@@ -5304,7 +5304,7 @@
         <v>330</v>
       </c>
       <c r="F50" s="3">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="G50" s="3">
         <v>117</v>
@@ -5399,7 +5399,7 @@
         <v>725</v>
       </c>
       <c r="F51" s="3">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="G51" s="3">
         <v>117</v>
@@ -5494,7 +5494,7 @@
         <v>107</v>
       </c>
       <c r="F52" s="3">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="G52" s="3">
         <v>117</v>
@@ -5589,7 +5589,7 @@
         <v>106</v>
       </c>
       <c r="F53" s="3">
-        <v>45</v>
+        <v>142</v>
       </c>
       <c r="G53" s="3">
         <v>117</v>
@@ -5684,7 +5684,7 @@
         <v>129</v>
       </c>
       <c r="F54" s="3">
-        <v>61</v>
+        <v>143</v>
       </c>
       <c r="G54" s="3">
         <v>125</v>
@@ -5779,7 +5779,7 @@
         <v>130</v>
       </c>
       <c r="F55" s="3">
-        <v>61</v>
+        <v>144</v>
       </c>
       <c r="G55" s="3">
         <v>125</v>
@@ -5874,7 +5874,7 @@
         <v>131</v>
       </c>
       <c r="F56" s="3">
-        <v>61</v>
+        <v>145</v>
       </c>
       <c r="G56" s="3">
         <v>125</v>
@@ -5969,7 +5969,7 @@
         <v>264</v>
       </c>
       <c r="F57" s="3">
-        <v>61</v>
+        <v>146</v>
       </c>
       <c r="G57" s="3">
         <v>125</v>
@@ -6064,7 +6064,7 @@
         <v>132</v>
       </c>
       <c r="F58" s="3">
-        <v>61</v>
+        <v>147</v>
       </c>
       <c r="G58" s="3">
         <v>125</v>
@@ -6159,7 +6159,7 @@
         <v>133</v>
       </c>
       <c r="F59" s="3">
-        <v>61</v>
+        <v>148</v>
       </c>
       <c r="G59" s="3">
         <v>125</v>
@@ -6254,7 +6254,7 @@
         <v>265</v>
       </c>
       <c r="F60" s="3">
-        <v>61</v>
+        <v>149</v>
       </c>
       <c r="G60" s="3">
         <v>125</v>
@@ -6349,7 +6349,7 @@
         <v>692</v>
       </c>
       <c r="F61" s="3">
-        <v>62</v>
+        <v>150</v>
       </c>
       <c r="G61" s="3">
         <v>126</v>
@@ -6444,7 +6444,7 @@
         <v>580</v>
       </c>
       <c r="F62" s="3">
-        <v>62</v>
+        <v>151</v>
       </c>
       <c r="G62" s="3">
         <v>126</v>
@@ -6537,7 +6537,7 @@
         <v>246</v>
       </c>
       <c r="F63" s="3">
-        <v>62</v>
+        <v>152</v>
       </c>
       <c r="G63" s="3">
         <v>126</v>
@@ -6632,7 +6632,7 @@
         <v>250</v>
       </c>
       <c r="F64" s="3">
-        <v>46</v>
+        <v>153</v>
       </c>
       <c r="G64" s="3">
         <v>130</v>
@@ -6727,7 +6727,7 @@
         <v>702</v>
       </c>
       <c r="F65" s="3">
-        <v>46</v>
+        <v>154</v>
       </c>
       <c r="G65" s="3">
         <v>101</v>
@@ -6822,7 +6822,7 @@
         <v>170</v>
       </c>
       <c r="F66" s="3">
-        <v>46</v>
+        <v>155</v>
       </c>
       <c r="G66" s="3">
         <v>101</v>

--- a/카테고리번호_기본.xlsx
+++ b/카테고리번호_기본.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jihun\Desktop\완성\★update\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\기린업데이트작업\기린컴퍼니\자동업데이트\2026\9\1\업데이트파일_20260831_1052\1단계_예제생성\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3986036C-234B-4F37-8369-2C92E75645D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E222AEA-67A1-4FF9-BE2D-71A590D4E79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27870" yWindow="2220" windowWidth="24225" windowHeight="17550" xr2:uid="{C7C98F17-E1B4-4C04-891E-7391719F0528}"/>
+    <workbookView xWindow="-27930" yWindow="2400" windowWidth="22845" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -27,6 +24,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,126 +36,96 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>원본</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>김윤지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>김하늘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>리린키즈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>모나마켓</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>곽충현</t>
   </si>
   <si>
     <t>박미리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>박소홍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>백종열</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>서송이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>설주연</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>신정임</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오마베</t>
+  </si>
+  <si>
+    <t>백성희</t>
+  </si>
+  <si>
+    <t>이하나</t>
   </si>
   <si>
     <t>차민주</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>최민기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>최지현</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>해피</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>스마트오토</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이하나</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이지민</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>이모이모</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오마베</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>백성희</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>문주하</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>문정희</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>김상희</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>신나겸</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>목윤희</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>최은경</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>현건주</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김다혜</t>
   </si>
   <si>
     <t>남부센</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>김다혜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>곽충현</t>
+    <t>홍일진</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -287,7 +256,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -312,6 +281,7 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -625,11 +595,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4EA2AF1-18E5-4619-BDBF-D08935AE7386}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE66"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="20" max="20" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.5" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -649,55 +619,55 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
         <v>30</v>
       </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="V1" t="s">
         <v>20</v>
-      </c>
-      <c r="O1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>12</v>
-      </c>
-      <c r="R1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S1" t="s">
-        <v>14</v>
-      </c>
-      <c r="T1" t="s">
-        <v>15</v>
-      </c>
-      <c r="U1" t="s">
-        <v>17</v>
-      </c>
-      <c r="V1" t="s">
-        <v>18</v>
       </c>
       <c r="W1" t="s">
         <v>21</v>
@@ -721,10 +691,10 @@
         <v>27</v>
       </c>
       <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
         <v>29</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.3">
@@ -789,7 +759,7 @@
         <v>50000419</v>
       </c>
       <c r="U2" s="3">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="V2" s="3">
         <v>55</v>
@@ -884,7 +854,7 @@
         <v>50000418</v>
       </c>
       <c r="U3" s="3">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="V3" s="3">
         <v>55</v>
@@ -979,7 +949,7 @@
         <v>50000420</v>
       </c>
       <c r="U4" s="3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="V4" s="3">
         <v>55</v>
@@ -1074,7 +1044,7 @@
         <v>50000270</v>
       </c>
       <c r="U5" s="3">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="V5" s="3">
         <v>55</v>
@@ -1169,7 +1139,7 @@
         <v>50000410</v>
       </c>
       <c r="U6" s="3">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="V6" s="3">
         <v>55</v>
@@ -1264,7 +1234,7 @@
         <v>50000535</v>
       </c>
       <c r="U7" s="3">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="V7" s="3">
         <v>56</v>
@@ -1359,7 +1329,7 @@
         <v>50000535</v>
       </c>
       <c r="U8" s="3">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="V8" s="3">
         <v>56</v>
@@ -1454,7 +1424,7 @@
         <v>50007114</v>
       </c>
       <c r="U9" s="3">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="V9" s="3">
         <v>56</v>
@@ -1549,7 +1519,7 @@
         <v>50000536</v>
       </c>
       <c r="U10" s="3">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="V10" s="3">
         <v>56</v>
@@ -1644,7 +1614,7 @@
         <v>50007114</v>
       </c>
       <c r="U11" s="3">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="V11" s="3">
         <v>56</v>
@@ -1739,7 +1709,7 @@
         <v>50000535</v>
       </c>
       <c r="U12" s="3">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="V12" s="3">
         <v>56</v>
@@ -1834,7 +1804,7 @@
         <v>50000535</v>
       </c>
       <c r="U13" s="3">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="V13" s="3">
         <v>56</v>
@@ -1929,7 +1899,7 @@
         <v>50000409</v>
       </c>
       <c r="U14" s="3">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="V14" s="3">
         <v>56</v>
@@ -2024,7 +1994,7 @@
         <v>50000535</v>
       </c>
       <c r="U15" s="3">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="V15" s="3">
         <v>56</v>
@@ -2119,7 +2089,7 @@
         <v>50000414</v>
       </c>
       <c r="U16" s="3">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="V16" s="3">
         <v>59</v>
@@ -2214,7 +2184,7 @@
         <v>50000411</v>
       </c>
       <c r="U17" s="3">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="V17" s="3">
         <v>57</v>
@@ -2309,7 +2279,7 @@
         <v>50007115</v>
       </c>
       <c r="U18" s="3">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="V18" s="3">
         <v>57</v>
@@ -2404,7 +2374,7 @@
         <v>50007116</v>
       </c>
       <c r="U19" s="3">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="V19" s="3">
         <v>57</v>
@@ -2499,7 +2469,7 @@
         <v>50000411</v>
       </c>
       <c r="U20" s="3">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="V20" s="3">
         <v>57</v>
@@ -2594,7 +2564,7 @@
         <v>50000411</v>
       </c>
       <c r="U21" s="3">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="V21" s="3">
         <v>57</v>
@@ -2689,7 +2659,7 @@
         <v>50000532</v>
       </c>
       <c r="U22" s="3">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="V22" s="3">
         <v>57</v>
@@ -2784,7 +2754,7 @@
         <v>50000411</v>
       </c>
       <c r="U23" s="3">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="V23" s="3">
         <v>57</v>
@@ -2879,7 +2849,7 @@
         <v>50000412</v>
       </c>
       <c r="U24" s="3">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="V24" s="3">
         <v>58</v>
@@ -2974,7 +2944,7 @@
         <v>50000271</v>
       </c>
       <c r="U25" s="3">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="V25" s="3">
         <v>60</v>
@@ -3069,7 +3039,7 @@
         <v>50000271</v>
       </c>
       <c r="U26" s="3">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="V26" s="3">
         <v>67</v>
@@ -3164,7 +3134,7 @@
         <v>50007124</v>
       </c>
       <c r="U27" s="3">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="V27" s="3">
         <v>66</v>
@@ -3259,7 +3229,7 @@
         <v>50000269</v>
       </c>
       <c r="U28" s="3">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="V28" s="3">
         <v>65</v>
@@ -3294,7 +3264,7 @@
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
-        <v>6136</v>
+        <v>6153</v>
       </c>
       <c r="B29" s="3">
         <v>110</v>
@@ -3354,7 +3324,7 @@
         <v>2004</v>
       </c>
       <c r="U29" s="3">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="V29" s="3">
         <v>28</v>
@@ -3449,7 +3419,7 @@
         <v>50000528</v>
       </c>
       <c r="U30" s="3">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="V30" s="3">
         <v>64</v>
@@ -3544,7 +3514,7 @@
         <v>50000528</v>
       </c>
       <c r="U31" s="3">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="V31" s="3">
         <v>75</v>
@@ -3639,7 +3609,7 @@
         <v>50000528</v>
       </c>
       <c r="U32" s="3">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="V32" s="3">
         <v>76</v>
@@ -3734,7 +3704,7 @@
         <v>50000528</v>
       </c>
       <c r="U33" s="3">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="V33" s="3">
         <v>77</v>
@@ -3829,7 +3799,7 @@
         <v>50000528</v>
       </c>
       <c r="U34" s="3">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="V34" s="3">
         <v>78</v>
@@ -3924,7 +3894,7 @@
         <v>50000528</v>
       </c>
       <c r="U35" s="3">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="V35" s="3">
         <v>79</v>
@@ -4019,7 +3989,7 @@
         <v>50005307</v>
       </c>
       <c r="U36" s="3">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="V36" s="3">
         <v>80</v>
@@ -4114,7 +4084,7 @@
         <v>50007138</v>
       </c>
       <c r="U37" s="3">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="V37" s="3">
         <v>81</v>
@@ -4209,7 +4179,7 @@
         <v>50000528</v>
       </c>
       <c r="U38" s="3">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="V38" s="3">
         <v>82</v>
@@ -4304,7 +4274,7 @@
         <v>50000531</v>
       </c>
       <c r="U39" s="3">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="V39" s="3">
         <v>83</v>
@@ -4399,7 +4369,7 @@
         <v>50004198</v>
       </c>
       <c r="U40" s="3">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="V40" s="3">
         <v>63</v>
@@ -4494,7 +4464,7 @@
         <v>50004198</v>
       </c>
       <c r="U41" s="3">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="V41" s="3">
         <v>84</v>
@@ -4589,7 +4559,7 @@
         <v>50004040</v>
       </c>
       <c r="U42" s="3">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="V42" s="3">
         <v>85</v>
@@ -4684,7 +4654,7 @@
         <v>50005465</v>
       </c>
       <c r="U43" s="3">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="V43" s="3">
         <v>86</v>
@@ -4779,7 +4749,7 @@
         <v>50004041</v>
       </c>
       <c r="U44" s="3">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="V44" s="3">
         <v>87</v>
@@ -4874,7 +4844,7 @@
         <v>50005466</v>
       </c>
       <c r="U45" s="3">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="V45" s="3">
         <v>88</v>
@@ -4969,7 +4939,7 @@
         <v>50000269</v>
       </c>
       <c r="U46" s="3">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="V46" s="3">
         <v>62</v>
@@ -5064,7 +5034,7 @@
         <v>50007111</v>
       </c>
       <c r="U47" s="3">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="V47" s="3">
         <v>89</v>
@@ -5159,7 +5129,7 @@
         <v>50000223</v>
       </c>
       <c r="U48" s="3">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="V48" s="3">
         <v>90</v>
@@ -5254,7 +5224,7 @@
         <v>50007140</v>
       </c>
       <c r="U49" s="3">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="V49" s="3">
         <v>91</v>
@@ -5349,7 +5319,7 @@
         <v>50004203</v>
       </c>
       <c r="U50" s="3">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="V50" s="3">
         <v>92</v>
@@ -5444,7 +5414,7 @@
         <v>50000352</v>
       </c>
       <c r="U51" s="3">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="V51" s="3">
         <v>93</v>
@@ -5539,7 +5509,7 @@
         <v>50000349</v>
       </c>
       <c r="U52" s="3">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V52" s="3">
         <v>94</v>
@@ -5634,7 +5604,7 @@
         <v>50000269</v>
       </c>
       <c r="U53" s="3">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="V53" s="3">
         <v>95</v>
@@ -5729,7 +5699,7 @@
         <v>50000419</v>
       </c>
       <c r="U54" s="3">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="V54" s="3">
         <v>68</v>
@@ -5824,7 +5794,7 @@
         <v>50000535</v>
       </c>
       <c r="U55" s="3">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="V55" s="3">
         <v>69</v>
@@ -5919,7 +5889,7 @@
         <v>50000411</v>
       </c>
       <c r="U56" s="3">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="V56" s="3">
         <v>70</v>
@@ -6014,7 +5984,7 @@
         <v>50000412</v>
       </c>
       <c r="U57" s="3">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="V57" s="3">
         <v>71</v>
@@ -6109,7 +6079,7 @@
         <v>50000414</v>
       </c>
       <c r="U58" s="3">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="V58" s="3">
         <v>72</v>
@@ -6204,7 +6174,7 @@
         <v>50000271</v>
       </c>
       <c r="U59" s="3">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="V59" s="3">
         <v>73</v>
@@ -6299,7 +6269,7 @@
         <v>50007138</v>
       </c>
       <c r="U60" s="3">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="V60" s="3">
         <v>74</v>
@@ -6394,7 +6364,7 @@
         <v>50000362</v>
       </c>
       <c r="U61" s="3">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="V61" s="3">
         <v>65</v>
@@ -6489,7 +6459,7 @@
         <v>50007119</v>
       </c>
       <c r="U62" s="3">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="V62" s="3">
         <v>65</v>
@@ -6582,7 +6552,7 @@
         <v>2004</v>
       </c>
       <c r="U63" s="3">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="V63" s="3">
         <v>65</v>
@@ -6677,7 +6647,7 @@
         <v>50007136</v>
       </c>
       <c r="U64" s="3">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="V64" s="3">
         <v>81</v>
@@ -6772,7 +6742,7 @@
         <v>50007138</v>
       </c>
       <c r="U65" s="3">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="V65" s="3">
         <v>81</v>
@@ -6867,7 +6837,7 @@
         <v>50007142</v>
       </c>
       <c r="U66" s="3">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="V66" s="3">
         <v>81</v>
@@ -6903,6 +6873,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>